--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2016/American_Aircraft_Cumulative_Statistics_2016.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2016/American_Aircraft_Cumulative_Statistics_2016.xlsx
@@ -13,33 +13,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="27" uniqueCount="27">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -121,10 +139,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="true"/>
+    <col min="1" max="1" width="9.140625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -144,40 +162,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -185,40 +203,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>2784842404</v>
+        <v>1113771945</v>
       </c>
       <c r="C2" s="0">
-        <v>3352677168</v>
+        <v>1466249067</v>
       </c>
       <c r="D2" s="0">
-        <v>580048</v>
+        <v>201963</v>
       </c>
       <c r="E2" s="0">
-        <v>177</v>
+        <v>99</v>
       </c>
       <c r="F2" s="0">
-        <v>20709</v>
+        <v>35406</v>
       </c>
       <c r="G2" s="0">
-        <v>3.5800000000000001</v>
+        <v>4.8799999999999999</v>
       </c>
       <c r="H2" s="0">
-        <v>8.4900000000000002</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="I2" s="0">
-        <v>83.060000000000002</v>
+        <v>75.959999999999994</v>
       </c>
       <c r="J2" s="0">
-        <v>912</v>
+        <v>418</v>
       </c>
       <c r="K2" s="0">
-        <v>2987</v>
+        <v>1699.24</v>
       </c>
       <c r="L2" s="0">
-        <v>16.829999999999998</v>
+        <v>17.16</v>
       </c>
       <c r="M2" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="3">
@@ -226,40 +244,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>7944268702</v>
+        <v>14979819171</v>
       </c>
       <c r="C3" s="0">
-        <v>9556952598</v>
+        <v>18551532232</v>
       </c>
       <c r="D3" s="0">
-        <v>510521</v>
+        <v>408804</v>
       </c>
       <c r="E3" s="0">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="F3" s="0">
-        <v>69514</v>
+        <v>180528</v>
       </c>
       <c r="G3" s="0">
-        <v>3.71</v>
+        <v>3.98</v>
       </c>
       <c r="H3" s="0">
-        <v>9.3800000000000008</v>
+        <v>9.1799999999999997</v>
       </c>
       <c r="I3" s="0">
-        <v>83.129999999999995</v>
+        <v>80.75</v>
       </c>
       <c r="J3" s="0">
-        <v>917</v>
+        <v>806</v>
       </c>
       <c r="K3" s="0">
-        <v>3008</v>
+        <v>2697.1300000000001</v>
       </c>
       <c r="L3" s="0">
-        <v>20.050000000000001</v>
+        <v>21.16</v>
       </c>
       <c r="M3" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -267,40 +285,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>11710040079</v>
+        <v>7944268702</v>
       </c>
       <c r="C4" s="0">
-        <v>13849819751</v>
+        <v>9556952598</v>
       </c>
       <c r="D4" s="0">
-        <v>557561</v>
+        <v>510521</v>
       </c>
       <c r="E4" s="0">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F4" s="0">
-        <v>98085</v>
+        <v>69514</v>
       </c>
       <c r="G4" s="0">
-        <v>3.9500000000000002</v>
+        <v>3.71</v>
       </c>
       <c r="H4" s="0">
-        <v>9.7300000000000004</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="I4" s="0">
-        <v>84.549999999999997</v>
+        <v>83.129999999999995</v>
       </c>
       <c r="J4" s="0">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="K4" s="0">
-        <v>3765</v>
+        <v>3008.04</v>
       </c>
       <c r="L4" s="0">
-        <v>24.43</v>
+        <v>20.050000000000001</v>
       </c>
       <c r="M4" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="5">
@@ -308,40 +326,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>7010799551</v>
+        <v>45102533081</v>
       </c>
       <c r="C5" s="0">
-        <v>8092062180</v>
+        <v>52727258910</v>
       </c>
       <c r="D5" s="0">
-        <v>866388</v>
+        <v>773127</v>
       </c>
       <c r="E5" s="0">
         <v>180</v>
       </c>
       <c r="F5" s="0">
-        <v>38766</v>
+        <v>234003</v>
       </c>
       <c r="G5" s="0">
-        <v>4.1500000000000004</v>
+        <v>3.4300000000000002</v>
       </c>
       <c r="H5" s="0">
-        <v>12.49</v>
+        <v>11.199999999999999</v>
       </c>
       <c r="I5" s="0">
-        <v>86.640000000000001</v>
+        <v>85.540000000000006</v>
       </c>
       <c r="J5" s="0">
-        <v>1160</v>
+        <v>1275</v>
       </c>
       <c r="K5" s="0">
-        <v>3525</v>
+        <v>3894.5</v>
       </c>
       <c r="L5" s="0">
-        <v>19.59</v>
+        <v>21.969999999999999</v>
       </c>
       <c r="M5" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -349,40 +367,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>31178732689</v>
+        <v>52352247749</v>
       </c>
       <c r="C6" s="0">
-        <v>36605087550</v>
+        <v>61719438739</v>
       </c>
       <c r="D6" s="0">
-        <v>769176</v>
+        <v>617133</v>
       </c>
       <c r="E6" s="0">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F6" s="0">
-        <v>188228</v>
+        <v>344647</v>
       </c>
       <c r="G6" s="0">
-        <v>3.96</v>
+        <v>3.4500000000000002</v>
       </c>
       <c r="H6" s="0">
-        <v>12.82</v>
+        <v>10.25</v>
       </c>
       <c r="I6" s="0">
-        <v>85.180000000000007</v>
+        <v>84.819999999999993</v>
       </c>
       <c r="J6" s="0">
-        <v>1296</v>
+        <v>1121</v>
       </c>
       <c r="K6" s="0">
-        <v>3257</v>
+        <v>3686.2199999999998</v>
       </c>
       <c r="L6" s="0">
-        <v>21.710000000000001</v>
+        <v>23.07</v>
       </c>
       <c r="M6" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -390,40 +408,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>11682085466</v>
+        <v>10983934416</v>
       </c>
       <c r="C7" s="0">
-        <v>13980219442</v>
+        <v>13533431674</v>
       </c>
       <c r="D7" s="0">
-        <v>887633</v>
+        <v>660167</v>
       </c>
       <c r="E7" s="0">
         <v>179</v>
       </c>
       <c r="F7" s="0">
-        <v>79739</v>
+        <v>43548</v>
       </c>
       <c r="G7" s="0">
-        <v>5.0599999999999996</v>
+        <v>2.1200000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>13.119999999999999</v>
+        <v>8.8399999999999999</v>
       </c>
       <c r="I7" s="0">
-        <v>83.560000000000002</v>
+        <v>81.159999999999997</v>
       </c>
       <c r="J7" s="0">
-        <v>980</v>
+        <v>1747</v>
       </c>
       <c r="K7" s="0">
-        <v>2714</v>
+        <v>4531.2399999999998</v>
       </c>
       <c r="L7" s="0">
-        <v>15.16</v>
+        <v>25.449999999999999</v>
       </c>
       <c r="M7" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -431,40 +449,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>15958600101</v>
+        <v>9717263237</v>
       </c>
       <c r="C8" s="0">
-        <v>18568985850</v>
+        <v>12511300380</v>
       </c>
       <c r="D8" s="0">
-        <v>522776</v>
+        <v>882320</v>
       </c>
       <c r="E8" s="0">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="F8" s="0">
-        <v>123157</v>
+        <v>22670</v>
       </c>
       <c r="G8" s="0">
-        <v>3.4700000000000002</v>
+        <v>1.6000000000000001</v>
       </c>
       <c r="H8" s="0">
-        <v>9.2100000000000009</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="I8" s="0">
-        <v>85.939999999999998</v>
+        <v>77.670000000000002</v>
       </c>
       <c r="J8" s="0">
-        <v>1005</v>
+        <v>2654</v>
       </c>
       <c r="K8" s="0">
-        <v>3772</v>
+        <v>6065.7200000000003</v>
       </c>
       <c r="L8" s="0">
-        <v>25.140000000000001</v>
+        <v>29.140000000000001</v>
       </c>
       <c r="M8" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -472,40 +490,286 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>88269368992</v>
+        <v>5361338642</v>
       </c>
       <c r="C9" s="0">
-        <v>104005804539</v>
+        <v>7351906289</v>
       </c>
       <c r="D9" s="0">
-        <v>660187</v>
+        <v>1346503</v>
       </c>
       <c r="E9" s="0">
-        <v>157</v>
+        <v>255</v>
       </c>
       <c r="F9" s="0">
-        <v>618198</v>
+        <v>9789</v>
       </c>
       <c r="G9" s="0">
-        <v>3.9199999999999999</v>
+        <v>1.79</v>
       </c>
       <c r="H9" s="0">
-        <v>10.960000000000001</v>
+        <v>11.550000000000001</v>
       </c>
       <c r="I9" s="0">
-        <v>84.870000000000005</v>
+        <v>72.920000000000002</v>
       </c>
       <c r="J9" s="0">
-        <v>1073</v>
+        <v>2962</v>
       </c>
       <c r="K9" s="0">
-        <v>3346</v>
+        <v>6359.6199999999999</v>
       </c>
       <c r="L9" s="0">
-        <v>21.329999999999998</v>
+        <v>25.07</v>
       </c>
       <c r="M9" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0">
+        <v>3760297907</v>
+      </c>
+      <c r="C10" s="0">
+        <v>5006064328</v>
+      </c>
+      <c r="D10" s="0">
+        <v>1526239</v>
+      </c>
+      <c r="E10" s="0">
+        <v>287</v>
+      </c>
+      <c r="F10" s="0">
+        <v>5156</v>
+      </c>
+      <c r="G10" s="0">
+        <v>1.5700000000000001</v>
+      </c>
+      <c r="H10" s="0">
+        <v>11.460000000000001</v>
+      </c>
+      <c r="I10" s="0">
+        <v>75.109999999999999</v>
+      </c>
+      <c r="J10" s="0">
+        <v>3391</v>
+      </c>
+      <c r="K10" s="0">
+        <v>7207.46</v>
+      </c>
+      <c r="L10" s="0">
+        <v>25.16</v>
+      </c>
+      <c r="M10" s="0">
+        <v>0.053999999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0">
+        <v>7002269839</v>
+      </c>
+      <c r="C11" s="0">
+        <v>8417341679</v>
+      </c>
+      <c r="D11" s="0">
+        <v>1417061</v>
+      </c>
+      <c r="E11" s="0">
+        <v>225</v>
+      </c>
+      <c r="F11" s="0">
+        <v>6804</v>
+      </c>
+      <c r="G11" s="0">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H11" s="0">
+        <v>12.43</v>
+      </c>
+      <c r="I11" s="0">
+        <v>83.189999999999998</v>
+      </c>
+      <c r="J11" s="0">
+        <v>5493</v>
+      </c>
+      <c r="K11" s="0">
+        <v>7162.6300000000001</v>
+      </c>
+      <c r="L11" s="0">
+        <v>31.800000000000001</v>
+      </c>
+      <c r="M11" s="0">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0">
+        <v>245976460</v>
+      </c>
+      <c r="C12" s="0">
+        <v>310309393</v>
+      </c>
+      <c r="D12" s="0">
+        <v>1410497</v>
+      </c>
+      <c r="E12" s="0">
+        <v>285</v>
+      </c>
+      <c r="F12" s="0">
+        <v>258</v>
+      </c>
+      <c r="G12" s="0">
+        <v>1.1699999999999999</v>
+      </c>
+      <c r="H12" s="0">
+        <v>10</v>
+      </c>
+      <c r="I12" s="0">
+        <v>79.269999999999996</v>
+      </c>
+      <c r="J12" s="0">
+        <v>4221</v>
+      </c>
+      <c r="K12" s="0">
+        <v>8960.4799999999996</v>
+      </c>
+      <c r="L12" s="0">
+        <v>31.440000000000001</v>
+      </c>
+      <c r="M12" s="0">
+        <v>0.064000000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0">
+        <v>16658057132</v>
+      </c>
+      <c r="C13" s="0">
+        <v>20975860080</v>
+      </c>
+      <c r="D13" s="0">
+        <v>1225225</v>
+      </c>
+      <c r="E13" s="0">
+        <v>250</v>
+      </c>
+      <c r="F13" s="0">
+        <v>19894</v>
+      </c>
+      <c r="G13" s="0">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="H13" s="0">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="I13" s="0">
+        <v>79.420000000000002</v>
+      </c>
+      <c r="J13" s="0">
+        <v>4225</v>
+      </c>
+      <c r="K13" s="0">
+        <v>9310.2199999999993</v>
+      </c>
+      <c r="L13" s="0">
+        <v>37.289999999999999</v>
+      </c>
+      <c r="M13" s="0">
+        <v>0.075999999999999998</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0">
+        <v>11860021217</v>
+      </c>
+      <c r="C14" s="0">
+        <v>15053123666</v>
+      </c>
+      <c r="D14" s="0">
+        <v>2105332</v>
+      </c>
+      <c r="E14" s="0">
+        <v>310</v>
+      </c>
+      <c r="F14" s="0">
+        <v>9996</v>
+      </c>
+      <c r="G14" s="0">
+        <v>1.3999999999999999</v>
+      </c>
+      <c r="H14" s="0">
+        <v>13.619999999999999</v>
+      </c>
+      <c r="I14" s="0">
+        <v>78.790000000000006</v>
+      </c>
+      <c r="J14" s="0">
+        <v>4859</v>
+      </c>
+      <c r="K14" s="0">
+        <v>10408.68</v>
+      </c>
+      <c r="L14" s="0">
+        <v>33.579999999999998</v>
+      </c>
+      <c r="M14" s="0">
+        <v>0.067000000000000004</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0">
+        <v>187081799498</v>
+      </c>
+      <c r="C15" s="0">
+        <v>227180769035</v>
+      </c>
+      <c r="D15" s="0">
+        <v>724845</v>
+      </c>
+      <c r="E15" s="0">
+        <v>163</v>
+      </c>
+      <c r="F15" s="0">
+        <v>982213</v>
+      </c>
+      <c r="G15" s="0">
+        <v>3.1299999999999999</v>
+      </c>
+      <c r="H15" s="0">
+        <v>10.210000000000001</v>
+      </c>
+      <c r="I15" s="0">
+        <v>82.349999999999994</v>
+      </c>
+      <c r="J15" s="0">
+        <v>1285</v>
+      </c>
+      <c r="K15" s="0">
+        <v>4364.9799999999996</v>
+      </c>
+      <c r="L15" s="0">
+        <v>24.870000000000001</v>
+      </c>
+      <c r="M15" s="0">
+        <v>0.060999999999999999</v>
       </c>
     </row>
   </sheetData>
